--- a/AAII_Financials/Yearly/RIOT_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/RIOT_YR_FIN.xlsx
@@ -1008,13 +1008,13 @@
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>138800</v>
+        <v>195500</v>
       </c>
       <c r="E14" s="3">
-        <v>53500</v>
+        <v>87200</v>
       </c>
       <c r="F14" s="3">
-        <v>-71900</v>
+        <v>-600</v>
       </c>
       <c r="G14" s="3">
         <v>393500</v>
@@ -1251,13 +1251,13 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-1500</v>
+        <v>-58200</v>
       </c>
       <c r="E20" s="3">
-        <v>-46100</v>
+        <v>-79800</v>
       </c>
       <c r="F20" s="3">
-        <v>-7000</v>
+        <v>-78200</v>
       </c>
       <c r="G20" s="3">
         <v>-98700</v>
@@ -1302,13 +1302,13 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-167600</v>
+        <v>-110900</v>
       </c>
       <c r="E21" s="3">
-        <v>350500</v>
+        <v>384200</v>
       </c>
       <c r="F21" s="3">
-        <v>117700</v>
+        <v>188900</v>
       </c>
       <c r="G21" s="3">
         <v>-20300</v>
@@ -1863,13 +1863,13 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>1500</v>
+        <v>58200</v>
       </c>
       <c r="E32" s="3">
-        <v>46100</v>
+        <v>79800</v>
       </c>
       <c r="F32" s="3">
-        <v>7000</v>
+        <v>78200</v>
       </c>
       <c r="G32" s="3">
         <v>98700</v>
